--- a/artfynd/A 44852-2026 artfynd.xlsx
+++ b/artfynd/A 44852-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153471</v>
       </c>
       <c r="B2" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153510</v>
       </c>
       <c r="B3" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153409</v>
       </c>
       <c r="B4" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153382</v>
       </c>
       <c r="B5" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
